--- a/output/full_scan/batch_seq0_2026-10-29.xlsx
+++ b/output/full_scan/batch_seq0_2026-10-29.xlsx
@@ -444,7 +444,7 @@
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>749.4157018460387</v>
+        <v>889.4157018460387</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>60.5</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.4273757482672607</v>
+        <v>0.4273757482252138</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8213</v>
+        <v>8089</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>682.731266391708</v>
+        <v>794.7316907406888</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>41.9</v>
+        <v>29</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>65.23482208367928</v>
+        <v>80.14585942110237</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>54.33482992709325</v>
+        <v>53.94210024842299</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.39098625356272</v>
+        <v>2.573169074068883</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2803452368371513</v>
+        <v>0.7603771596204196</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8215</v>
+        <v>8299</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>641.5311850911925</v>
+        <v>763.3821249965068</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>29.05</v>
+        <v>2050</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>56.15595140879029</v>
+        <v>54.3929714903925</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>30.26885628153543</v>
+        <v>14.90073998670725</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.80584020441449</v>
+        <v>1.167040699662988</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.02903492783776729</v>
+        <v>7.414212833325948</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, liquidity_ok, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8089</v>
+        <v>8213</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>614.7316907406888</v>
+        <v>762.731266391708</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>29</v>
+        <v>41.9</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>80.14585935499943</v>
+        <v>65.2348220699369</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>53.94210014320221</v>
+        <v>54.33482992097358</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.573169074068883</v>
+        <v>1.39098625356272</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.7603771597605913</v>
+        <v>0.2803452368091244</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8277</v>
+        <v>8162</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>592.4120760963485</v>
+        <v>753.6170420799921</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.00775065631917</v>
+        <v>56.87075356945939</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>36.46028949018805</v>
+        <v>21.75413055381614</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.2849753520368781</v>
+        <v>1.772841923111925</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.2594757323095989</v>
+        <v>0.1938235465053211</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8299</v>
+        <v>8215</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>583.3821249965067</v>
+        <v>666.5311850911925</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2050</v>
+        <v>29.05</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>54.39297154056644</v>
+        <v>56.15595141815111</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>14.9007401022286</v>
+        <v>30.26885628849016</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.167040699662988</v>
+        <v>1.80584020441449</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>7.41421282001</v>
+        <v>-0.02903492776768157</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, obv_uptrend, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8431</v>
+        <v>8081</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>576.65588091299</v>
+        <v>665.1245409790407</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>60.8</v>
+        <v>271.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45.43327159036841</v>
+        <v>63.25479228349387</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25.12223051961852</v>
+        <v>17.28306986758585</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2467084743591382</v>
+        <v>0.5492491414749104</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.9160327671433575</v>
+        <v>0.7865191525704924</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8050</v>
+        <v>8042</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>570.6426826344635</v>
+        <v>658.0716988679361</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>62.2</v>
+        <v>141</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>50.31542875171381</v>
+        <v>56.50198140101823</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27.5051670785798</v>
+        <v>41.20060954158265</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5093382448502116</v>
+        <v>0.5678910610778967</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.2976420262622179</v>
+        <v>-0.5663644078387122</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8042</v>
+        <v>8070</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>538.0716988679361</v>
+        <v>652.1768323039524</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>141</v>
+        <v>50.7</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.50198140556918</v>
+        <v>50.27290020864524</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>41.20060950526862</v>
+        <v>15.07863167784776</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5678910610778967</v>
+        <v>1.692427216639134</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.5663644080209451</v>
+        <v>-0.1336114818173971</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8227</v>
+        <v>8291</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>532.8868412049898</v>
+        <v>632.159832962918</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>250.5</v>
+        <v>30.85</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>41.82405053624676</v>
+        <v>61.02221017842647</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>29.6423695576874</v>
+        <v>18.09772799812332</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.739000956440363</v>
+        <v>4.175576666611785</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-12.68706393754744</v>
+        <v>0.838972664174122</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>9103</v>
+        <v>8455</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>505.7437705207252</v>
+        <v>626.4598758827306</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5.48</v>
+        <v>26.45</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>48.73160740448754</v>
+        <v>52.8871653306857</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>25.6363915417165</v>
+        <v>8.594029870863588</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.1707672995217567</v>
+        <v>3.745987588273058</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.06537765482128219</v>
+        <v>0.8827207717077992</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8162</v>
+        <v>8463</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>503.6170420799921</v>
+        <v>625.7457198635193</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>21.55</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>56.87075371998963</v>
+        <v>57.83707707291867</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>21.75413054154372</v>
+        <v>23.99276309042737</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.772841923111925</v>
+        <v>0.3801725398450066</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,11 +1153,11 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1938235458044761</v>
+        <v>0.03146911664065453</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>501.2973195473932</v>
+        <v>596.2973195473933</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>153</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>51.55436582085007</v>
+        <v>51.55436578131762</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>25.5973041175296</v>
+        <v>25.59730416258697</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0.6271311205138246</v>
@@ -1200,37 +1200,37 @@
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.091920141107057</v>
+        <v>1.091920142088271</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8059</v>
+        <v>8466</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>494.038748512868</v>
+        <v>590.6505218369999</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16.15</v>
+        <v>15.35</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46.10731311844779</v>
+        <v>54.95232657795409</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.58310294419642</v>
+        <v>15.21926341178903</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5565850337271088</v>
+        <v>1.707622935510553</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>3</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.2649935633420934</v>
+        <v>0.04034429538769117</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>volume_break, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8996</v>
+        <v>8926</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>493.5582103270859</v>
+        <v>570.1452834287553</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1545</v>
+        <v>57.7</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,66 +1294,66 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.0973119849321</v>
+        <v>46.2741932810744</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>31.62736008176968</v>
+        <v>11.38109529461361</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7196452885880719</v>
+        <v>0.4166049882521248</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-23.23236029546413</v>
+        <v>-0.1309346508820654</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8908</v>
+        <v>8271</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>欣雄</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>490.8642278537412</v>
+        <v>561.6500004373997</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>40.2</v>
+        <v>189</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>53.9736162612976</v>
+        <v>44.2695241701657</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15.22478471745501</v>
+        <v>24.54682235215088</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.760617295114085</v>
+        <v>1.758100005157399</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>1</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.005565450760146473</v>
+        <v>0.5748056638729526</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8462</v>
+        <v>8464</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>487.4382420987189</v>
+        <v>560.3320673248371</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>157.5</v>
+        <v>373</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>44.88010392693821</v>
+        <v>53.96141295498124</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>26.59068933630647</v>
+        <v>12.07989876374459</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3438242098718876</v>
+        <v>1.004755059328197</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.6419373837031955</v>
+        <v>0.905087686824491</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8070</v>
+        <v>9103</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>482.1768323039524</v>
+        <v>555.7437705207251</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>50.7</v>
+        <v>5.48</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>50.27290029170128</v>
+        <v>48.73160743223457</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15.07863170547864</v>
+        <v>25.63639155319647</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.692427216639134</v>
+        <v>0.1707672995217567</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.1336114820276573</v>
+        <v>-0.06537765482969154</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8271</v>
+        <v>8050</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>481.6500004373998</v>
+        <v>550.6426826344635</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>189</v>
+        <v>62.2</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>44.2695242428135</v>
+        <v>50.31542875171381</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>24.54682242421582</v>
+        <v>27.50516708240849</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.758100005157399</v>
+        <v>0.5093382448502116</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.5748056630038949</v>
+        <v>-0.2976420264584521</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8455</v>
+        <v>8996</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>476.4598758827306</v>
+        <v>548.5582103270858</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>26.45</v>
+        <v>1545</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>52.8871653346032</v>
+        <v>51.09731198650692</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>8.59402986689158</v>
+        <v>31.62736001552343</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3.745987588273058</v>
+        <v>0.7196452885880719</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.8827207715676284</v>
+        <v>-23.23236029364183</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8081</v>
+        <v>8088</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>475.1245409790408</v>
+        <v>540.8284794768448</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>271.5</v>
+        <v>42.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>63.25479216091423</v>
+        <v>48.2369033554447</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>17.28306978956794</v>
+        <v>11.68394934248442</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5492491414749104</v>
+        <v>0.9901005489059718</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.7865191529909716</v>
+        <v>9.325421688166635e-05</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8463</v>
+        <v>9912</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>460.7457198635192</v>
+        <v>507.6223834879289</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>21.55</v>
+        <v>13.4</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>57.83707709955834</v>
+        <v>53.00430562965758</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>23.99276322209819</v>
+        <v>20.40683467671348</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3801725398450066</v>
+        <v>0.4125278781467386</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.03146911661262014</v>
+        <v>0.2081453333601103</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8111</v>
+        <v>8150</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>456.8360043402225</v>
+        <v>504.5709653995971</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>78.3</v>
+        <v>97.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>48.66784848030708</v>
+        <v>42.27004890596212</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.69509207681092</v>
+        <v>26.88341088314779</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4366106800880464</v>
+        <v>0.2904847257856227</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.477480892888565</v>
+        <v>-2.879709480968899</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8291</v>
+        <v>8277</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>452.159832962918</v>
+        <v>502.4120760963485</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>30.85</v>
+        <v>15.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>61.02221017842647</v>
+        <v>65.00775047699695</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>18.09772799812332</v>
+        <v>36.46028966845608</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4.175576666611785</v>
+        <v>0.2849753520368781</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.838972664174122</v>
+        <v>-0.2594757318051217</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8150</v>
+        <v>8341</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>449.5709653995971</v>
+        <v>500.2055272482152</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>97.2</v>
+        <v>76</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>42.27004890162064</v>
+        <v>55.86895615691955</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>26.88341090811615</v>
+        <v>20.89013106988652</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2904847257856227</v>
+        <v>0.6946619002692663</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-2.879709481081047</v>
+        <v>0.3608274374490508</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8341</v>
+        <v>8442</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>445.2055272482153</v>
+        <v>492.7553175143401</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>76</v>
+        <v>47.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.86895606224904</v>
+        <v>55.08970487976689</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20.89013105382634</v>
+        <v>16.91321627233631</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.6946619002692663</v>
+        <v>0.2552331043082277</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,51 +1895,51 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.3608274375331537</v>
+        <v>-0.03569243615692697</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8442</v>
+        <v>8908</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>欣雄</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>442.7553175143401</v>
+        <v>490.8642278537418</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="G28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.08970496709433</v>
+        <v>53.97361644428725</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>16.91321634917269</v>
+        <v>15.22478478855913</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.2552331043082277</v>
+        <v>0.760617295114085</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.03569243618495821</v>
+        <v>-0.005565450808193428</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8068</v>
+        <v>8112</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>441.2196082593334</v>
+        <v>490.8573522497494</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>17.75</v>
+        <v>83.7</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>49.76485222940091</v>
+        <v>45.95584632163884</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>30.51406188387829</v>
+        <v>10.68106672854985</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3891453482239131</v>
+        <v>0.65743062911548</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.09977794396388392</v>
+        <v>0.1898790123825965</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8112</v>
+        <v>8431</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>435.8573522497494</v>
+        <v>486.65588091299</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>83.7</v>
+        <v>60.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45.95584634120525</v>
+        <v>45.43327158341933</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>10.68106677315362</v>
+        <v>25.12223059650692</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.65743062911548</v>
+        <v>0.2467084743591382</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1898790124246464</v>
+        <v>-0.9160327671293409</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>9912</v>
+        <v>8163</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>427.622383487929</v>
+        <v>485.3194257681207</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>13.4</v>
+        <v>29.2</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>53.0043056188767</v>
+        <v>46.3887097824803</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.40683467671348</v>
+        <v>20.5757523906495</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.4125278781467386</v>
+        <v>0.4106667377604783</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2081453333741274</v>
+        <v>0.02726568292060416</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8086</v>
+        <v>8047</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>427.0318153234093</v>
+        <v>470.1531607877332</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>122</v>
+        <v>55.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>47.58519638294842</v>
+        <v>56.31724264347104</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>20.24046076485892</v>
+        <v>8.4985217884772</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4483888677850135</v>
+        <v>0.0618186470260342</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-1.940790006786381</v>
+        <v>1.053059160602675</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>rsi_strong, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8088</v>
+        <v>8201</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>420.8284794768085</v>
+        <v>467.1701267246223</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>42.7</v>
+        <v>15.9</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>48.23690332193397</v>
+        <v>54.39512940239518</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>11.68394935420948</v>
+        <v>34.84281462571966</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.9901005489059718</v>
+        <v>0.1751248115507144</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,11 +2213,11 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>9.325337586379989e-05</v>
+        <v>-0.09652615231680572</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>413.2447286718117</v>
+        <v>458.2447286718117</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>161</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>42.48273479132045</v>
+        <v>42.48273470681904</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15.35877375955175</v>
+        <v>15.35877377153094</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1.806034502644881</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.3005202958962929</v>
+        <v>-0.3005202942142393</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8201</v>
+        <v>8374</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>412.1701267246223</v>
+        <v>450.5826513307715</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>15.9</v>
+        <v>71.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>54.39512922198256</v>
+        <v>38.20360613127813</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>34.84281458079305</v>
+        <v>17.47480112913079</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.1751248115507144</v>
+        <v>1.331932622875736</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0965261522607388</v>
+        <v>0.02535222424957539</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8289</v>
+        <v>8454</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>410.8322342102564</v>
+        <v>447.8258576002141</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>46.35</v>
+        <v>248</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>41.8769517420074</v>
+        <v>51.58446495718681</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25.48124206739712</v>
+        <v>13.37449431466054</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.2049164686791258</v>
+        <v>0.8354452454109371</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.220379985108076</v>
+        <v>0.5482054906296173</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8084</v>
+        <v>8096</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>407.5325737245332</v>
+        <v>447.5124644721981</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>11.4</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>15.83549195798061</v>
+        <v>43.76594137893876</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>65.9178166967589</v>
+        <v>30.93973891103458</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5876605917568199</v>
+        <v>0.9403346990283441</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4736715398672811</v>
+        <v>0.6054892628572608</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8163</v>
+        <v>8227</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>405.3194257681166</v>
+        <v>442.8868412049898</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>29.2</v>
+        <v>250.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46.38870970931139</v>
+        <v>41.82405055776211</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>20.57575239064951</v>
+        <v>29.6423696125069</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4106667377604783</v>
+        <v>0.739000956440363</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.02726568304676469</v>
+        <v>-12.68706393838845</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8466</v>
+        <v>8367</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>400.6505218369999</v>
+        <v>439.7864084837811</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>15.35</v>
+        <v>41.2</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.95232659726419</v>
+        <v>52.69695037543449</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15.21926340437576</v>
+        <v>15.57968086191222</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.707622935510553</v>
+        <v>0.4736511271716388</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.04034429535965642</v>
+        <v>-0.04216584512137363</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8926</v>
+        <v>8423</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>400.1452834287553</v>
+        <v>438.8918219134684</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>57.7</v>
+        <v>18</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>46.27419320524814</v>
+        <v>52.60348768591086</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11.3810952946136</v>
+        <v>28.79871051913765</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4166049882521248</v>
+        <v>0.2422032246931227</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.1309346509661681</v>
+        <v>0.001453949981721908</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8045</v>
+        <v>8103</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>397.9856429186143</v>
+        <v>432.0415604338958</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>53.1</v>
+        <v>106.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46.63892614375298</v>
+        <v>44.97783056412523</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>17.63947432054461</v>
+        <v>21.60417034483602</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.01682259049193</v>
+        <v>0.4820305487861239</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.1071483785341122</v>
+        <v>-0.9548907074594242</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8454</v>
+        <v>8068</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>397.8258576002139</v>
+        <v>421.2196082593334</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>248</v>
+        <v>17.75</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.58446505541355</v>
+        <v>49.76485226441181</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13.37449435822713</v>
+        <v>30.51406190401252</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.8354452454109371</v>
+        <v>0.3891453482239131</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.5482054903492692</v>
+        <v>-0.09977794396388392</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8367</v>
+        <v>8046</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>384.7864084837811</v>
+        <v>420.6682839268123</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>41.2</v>
+        <v>1250</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.69695024846337</v>
+        <v>44.82816757510045</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>15.57968090459569</v>
+        <v>19.5648379166849</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4736511271716388</v>
+        <v>0.5943531999061906</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.0421658450793217</v>
+        <v>-26.6012884369568</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8383</v>
+        <v>8462</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>381.0159350734116</v>
+        <v>417.4382420987189</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>68.8</v>
+        <v>157.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.8313054893873</v>
+        <v>44.88010407986338</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>17.43499634732506</v>
+        <v>26.59068931214203</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6860385799393174</v>
+        <v>0.3438242098718876</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0400592611135735</v>
+        <v>0.6419373838433593</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8464</v>
+        <v>8111</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>366.2245821181298</v>
+        <v>416.8360043402225</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>373</v>
+        <v>78.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.96141279581588</v>
+        <v>48.66784846775425</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12.07989869219217</v>
+        <v>23.69509202003358</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3332929530733338</v>
+        <v>0.4366106800880464</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.9050876855629509</v>
+        <v>-1.477480892341899</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8046</v>
+        <v>8467</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>365.6682839268122</v>
+        <v>415.4398375423343</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1250</v>
+        <v>100</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>44.8281675814304</v>
+        <v>55.65908186651331</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>19.56483804395322</v>
+        <v>18.66931407782448</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5943531999061906</v>
+        <v>0.6638039715446098</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-26.60128843751755</v>
+        <v>0.3755786749764862</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8467</v>
+        <v>8478</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>360.4398375423352</v>
+        <v>412.1530150752837</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>55.65908150983766</v>
+        <v>53.70803993725417</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>18.66931406059976</v>
+        <v>21.01562500572009</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6638039715446098</v>
+        <v>1.23047580924437</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,51 +2955,51 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.3755786765183609</v>
+        <v>0.6265068145239099</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8183</v>
+        <v>8059</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>355.8634049635208</v>
+        <v>404.038748512868</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>28.2</v>
+        <v>16.15</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G48" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>44.90268885457892</v>
+        <v>46.10731296708834</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>19.14537787982888</v>
+        <v>21.5831029535397</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.870816255095116</v>
+        <v>0.5565850337271088</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.06862061267980896</v>
+        <v>-0.2649935632219826</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>9105</v>
+        <v>8039</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>353.2795384837154</v>
+        <v>396.86961434944</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>8.44</v>
+        <v>266</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.05128199408579</v>
+        <v>45.10501039587756</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>29.9782992204164</v>
+        <v>17.1668186564038</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4853964792877657</v>
+        <v>0.424669671898029</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.05753407286534389</v>
+        <v>-4.397769700219095</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8103</v>
+        <v>8429</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>352.0415604338958</v>
+        <v>393.0388734739821</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>106.5</v>
+        <v>5.9</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>44.97783057796312</v>
+        <v>44.1302341999347</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21.604170384637</v>
+        <v>14.6375688063342</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4820305487861239</v>
+        <v>1.677058290372585</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.9548907074113804</v>
+        <v>0.0003146117220774892</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8044</v>
+        <v>8289</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>351.7808296226744</v>
+        <v>390.8322342102564</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>23.8</v>
+        <v>46.35</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>43.0414377262566</v>
+        <v>41.8769517374876</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>22.38995641898124</v>
+        <v>25.48124200526421</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7827567848802739</v>
+        <v>0.2049164686791258</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1022818585012777</v>
+        <v>-1.220379985080039</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8423</v>
+        <v>8210</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>343.8918219134684</v>
+        <v>388.0979490204571</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>18</v>
+        <v>756</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.60348738002683</v>
+        <v>28.77361696589598</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>28.7987105996394</v>
+        <v>31.1388061726016</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2422032246931227</v>
+        <v>0.7132376215542282</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.001453950009755627</v>
+        <v>-4.450776740663599</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8429</v>
+        <v>8084</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>343.0388734739821</v>
+        <v>387.5325737245332</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>5.9</v>
+        <v>11.4</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.13023417360123</v>
+        <v>15.83549198136497</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>14.6375688045292</v>
+        <v>65.91781667904752</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.677058290372585</v>
+        <v>0.5876605917568199</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0003146117276840894</v>
+        <v>0.4736715397551432</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8210</v>
+        <v>8086</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>338.0979490204571</v>
+        <v>387.0318153234094</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>756</v>
+        <v>122</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>28.77361720684669</v>
+        <v>47.585196400438</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>31.13880615742391</v>
+        <v>20.24046067442249</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7132376215542282</v>
+        <v>0.4483888677850135</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-4.450776751036152</v>
+        <v>-1.940790006506039</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8091</v>
+        <v>8249</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>332.5317688250994</v>
+        <v>381.5125342969958</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>202</v>
+        <v>39.85</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>38.62302740410605</v>
+        <v>49.78155390502156</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>15.5081914328934</v>
+        <v>13.0101252648305</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5597501163000628</v>
+        <v>0.4999869913262592</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-1.863754777178606</v>
+        <v>0.06516328628093607</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8478</v>
+        <v>8443</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>332.1530150752844</v>
+        <v>381.2470869465864</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>142</v>
+        <v>11.1</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>53.7080398301009</v>
+        <v>51.4296669317818</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.01562496153671</v>
+        <v>26.4026538723896</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.23047580924437</v>
+        <v>0.1170833504949408</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.6265068139632146</v>
+        <v>0.1404042677743896</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8443</v>
+        <v>8261</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>331.2470869465864</v>
+        <v>378.5751380049269</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>11.1</v>
+        <v>147.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.4296669317818</v>
+        <v>36.10754889200227</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.4026538723896</v>
+        <v>23.5386053008057</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.1170833504949408</v>
+        <v>0.3161255970805689</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1404042677743896</v>
+        <v>-2.242799916997735</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8040</v>
+        <v>8932</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>327.7911562963183</v>
+        <v>369.7237053021105</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>77.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>40.91793921035929</v>
+        <v>47.01474725019801</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>22.04370094666819</v>
+        <v>11.57093139947311</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.306241890115925</v>
+        <v>0.9015637378633969</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.40349509247433</v>
+        <v>-0.004670242490102838</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8096</v>
+        <v>8383</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>327.5124644721981</v>
+        <v>361.0159350734116</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>85.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>43.76594142367797</v>
+        <v>49.83130549229683</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>30.93973899506548</v>
+        <v>17.43499642659875</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.9403346990283441</v>
+        <v>0.6860385799393174</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,48 +3591,48 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.605489262534868</v>
+        <v>0.04005926098742374</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8074</v>
+        <v>8183</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>320.1932227775094</v>
+        <v>355.8634049635207</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>53.1</v>
+        <v>28.2</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45.60468983499559</v>
+        <v>44.90268808524906</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>23.97051052014859</v>
+        <v>19.14537750243876</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.2807177573296061</v>
+        <v>1.870816255095116</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.3433423155785419</v>
+        <v>0.06862061359425359</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8261</v>
+        <v>8109</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>318.575138004927</v>
+        <v>349.2896562170723</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>147.5</v>
+        <v>132</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>36.10754888171707</v>
+        <v>47.53429589761067</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>23.53860524779316</v>
+        <v>15.05938476748594</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3161255970805689</v>
+        <v>0.8583796840592951</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-2.242799917222031</v>
+        <v>-0.5817557737684991</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8438</v>
+        <v>8034</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>316.4881878066753</v>
+        <v>343.9692841626074</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>67.7</v>
+        <v>19.65</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>36.50467572297522</v>
+        <v>50.14830652159532</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>27.45108820225128</v>
+        <v>14.13722751609245</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4452489275511506</v>
+        <v>1.489392048493493</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.226994753739395</v>
+        <v>0.05620572509778182</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8182</v>
+        <v>8045</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>313.4367636396439</v>
+        <v>337.985642918615</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>37.1</v>
+        <v>53.1</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>39.37269015371109</v>
+        <v>46.63892609681736</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>16.8603271206501</v>
+        <v>17.63947434687804</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.1442728522489113</v>
+        <v>2.01682259049193</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.6022940315719141</v>
+        <v>-0.1071483779734306</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8093</v>
+        <v>8044</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>311.3988411282929</v>
+        <v>331.7808296226744</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>26</v>
+        <v>23.8</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>50.15503037607135</v>
+        <v>43.04143774188285</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.51589980179179</v>
+        <v>22.38995643338855</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5288388470148266</v>
+        <v>0.7827567848802739</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1494600054856546</v>
+        <v>-0.1022818585713606</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8249</v>
+        <v>8131</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>306.5125342970043</v>
+        <v>319.6685695281466</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>39.85</v>
+        <v>61.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>49.78155382661415</v>
+        <v>46.35174514184138</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13.01012525595128</v>
+        <v>13.1466994487469</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4999869913262592</v>
+        <v>0.4150783436837771</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,11 +3909,11 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0651632861127326</v>
+        <v>-0.3837084687292877</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>302.1442332931363</v>
+        <v>317.1442332931363</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>25.3</v>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>44.03875622574552</v>
+        <v>44.03875699403938</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11.85998224942859</v>
+        <v>11.85998234202595</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.8340627958401508</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3966,27 +3966,27 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8234</v>
+        <v>8091</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>298.9492943952395</v>
+        <v>312.5317688251027</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>61.1</v>
+        <v>202</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>42.5679732085954</v>
+        <v>38.62302745913119</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>13.02154037951885</v>
+        <v>15.5081914328934</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.169037812084542</v>
+        <v>0.5597501163000628</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.01976645182576192</v>
+        <v>-1.86375477647776</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8047</v>
+        <v>8040</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>290.1531607877319</v>
+        <v>307.7911562963183</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>55.9</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>56.31724262864255</v>
+        <v>40.91793915734005</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>8.498521812822569</v>
+        <v>22.04370097878997</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.0618186470260342</v>
+        <v>0.306241890115925</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>1.053059160402483</v>
+        <v>-1.403495092362205</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8171</v>
+        <v>8074</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>287.8132855377571</v>
+        <v>300.1932227775093</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>20.25</v>
+        <v>53.1</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>42.25719955153333</v>
+        <v>45.60468982462356</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>23.42403198973768</v>
+        <v>23.97051055855595</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.426232126573298</v>
+        <v>0.2807177573296061</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1861513709046025</v>
+        <v>-0.3433423154243541</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8374</v>
+        <v>9105</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>285.5826513307716</v>
+        <v>293.2795384837154</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>71.2</v>
+        <v>8.44</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>38.2036061764336</v>
+        <v>44.05128197938073</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.47480110702259</v>
+        <v>29.97829931954568</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.331932622875736</v>
+        <v>0.4853964792877657</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.02535222396923498</v>
+        <v>-0.05753407287095058</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8121</v>
+        <v>8093</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>279.9535162816024</v>
+        <v>291.3988411282929</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>29.1</v>
+        <v>26</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>44.41690187611539</v>
+        <v>50.15503041689301</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>21.10707071825412</v>
+        <v>14.51589992790213</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.1929462306030016</v>
+        <v>0.5288388470148266</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.457585465965182</v>
+        <v>-0.1494600055577224</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8390</v>
+        <v>8064</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>278.3379560368466</v>
+        <v>287.4755501936752</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>83</v>
+        <v>117.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>25.85748743602187</v>
+        <v>45.09984814510684</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>22.20995391455694</v>
+        <v>14.00900251968707</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.51770872809185</v>
+        <v>0.2915592246543577</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.5877094394207547</v>
+        <v>-1.54839914552958</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8155</v>
+        <v>8234</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>275.5636687020485</v>
+        <v>278.9492943952398</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>285</v>
+        <v>61.1</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>38.26397618041084</v>
+        <v>42.56797301274123</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.93982032606512</v>
+        <v>13.02154037951886</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.7368571956086573</v>
+        <v>1.169037812084542</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-2.815559563648881</v>
+        <v>-0.01976645143328298</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8101</v>
+        <v>8067</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>272.7461951481095</v>
+        <v>275.006997309318</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>12.85</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>35.75252547721664</v>
+        <v>53.78200842052836</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>30.41452042907202</v>
+        <v>17.13649663593052</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.132456677495131</v>
+        <v>1.946107028310225</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.03012462902321106</v>
+        <v>0.3707256804881088</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8131</v>
+        <v>8171</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>264.6685695281466</v>
+        <v>267.8132855377571</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>61.7</v>
+        <v>20.25</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46.35174514184138</v>
+        <v>42.25719961695098</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.14669948448181</v>
+        <v>23.42403193889794</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4150783436837771</v>
+        <v>0.426232126573298</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.383708468855436</v>
+        <v>-0.1861513709606723</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>9136</v>
+        <v>9930</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>261.1123756699134</v>
+        <v>265.0958312161078</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>40.86275316982852</v>
+        <v>36.97314189652808</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>26.16030379531184</v>
+        <v>24.7751376284389</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.976095081190688</v>
+        <v>0.7417113621673289</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0529624442035283</v>
+        <v>0.0674122889146449</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8043</v>
+        <v>8390</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>256.9048684450477</v>
+        <v>258.3379560368465</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>40.05061063525381</v>
+        <v>25.85748737957432</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14.24391219317048</v>
+        <v>22.20995391455694</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3631573251636229</v>
+        <v>1.51770872809185</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-1.413481859635392</v>
+        <v>-0.5877094392805846</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8109</v>
+        <v>8438</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>254.2896562170724</v>
+        <v>256.4881878066753</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>132</v>
+        <v>67.7</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>47.53429614768494</v>
+        <v>36.50467583246193</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15.05938487865</v>
+        <v>27.45108826165898</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8583796840592951</v>
+        <v>0.4452489275511506</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.581755774889857</v>
+        <v>-1.22699475372537</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8487</v>
+        <v>8155</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>253.1934888789405</v>
+        <v>255.5636687020485</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>2.615589337875448</v>
+        <v>38.26397619573616</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>20.53372485720499</v>
+        <v>19.93982018170354</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.0133436018664569</v>
+        <v>0.7368571956086573</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-4.455506510828632</v>
+        <v>-2.815559563648881</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8039</v>
+        <v>8182</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>251.8696143494399</v>
+        <v>253.4367636396439</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>266</v>
+        <v>37.1</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45.10501040433262</v>
+        <v>39.37269015371109</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>17.16681892799058</v>
+        <v>16.86032710992642</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.424669671898029</v>
+        <v>0.1442728522489113</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-4.397769700807778</v>
+        <v>-0.6022940315859298</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8411</v>
+        <v>8121</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>249.9952564605461</v>
+        <v>239.9535162816019</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>11.05</v>
+        <v>29.1</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>24.99537732135066</v>
+        <v>44.41690201031859</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>54.13570850741753</v>
+        <v>21.10707079098164</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.1396830556684275</v>
+        <v>0.1929462306030016</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.01012993523577566</v>
+        <v>-0.4575854661614192</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8932</v>
+        <v>8043</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>249.7237053021103</v>
+        <v>236.9048684450477</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>126</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>47.01474867660146</v>
+        <v>40.0506106522576</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.57093105882032</v>
+        <v>14.24391217990226</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.9015637378633969</v>
+        <v>0.3631573251636229</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,11 +4810,11 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.004670250657791364</v>
+        <v>-1.413481859635392</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>248.7877682870574</v>
+        <v>228.7877682870574</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>12.15</v>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>39.06734316718279</v>
+        <v>39.06734382061533</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>11.41195665135454</v>
+        <v>11.41195668792469</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.3502335212997383</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.01352705400799345</v>
+        <v>-0.01352705399397841</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8404</v>
+        <v>8477</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>246.5772431106191</v>
+        <v>224.5973402551514</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>36.38610967237447</v>
+        <v>6.287105055645512</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>25.00717952098518</v>
+        <v>45.57122919713481</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.9595825616131861</v>
+        <v>5.830053927998834e-05</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.04321297207991615</v>
+        <v>-0.8463986710575057</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8477</v>
+        <v>8147</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>244.5973402551513</v>
+        <v>223.6701148103911</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>6.287105037280384</v>
+        <v>44.55493677998767</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45.57122919713481</v>
+        <v>20.40187124590321</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>5.830053927998834e-05</v>
+        <v>1.256035025920486</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.8463986710154555</v>
+        <v>-1.363745660495133</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8147</v>
+        <v>8080</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>243.6701148103913</v>
+        <v>223.3378781593587</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>128</v>
+        <v>28.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.55493696905947</v>
+        <v>52.14029396787578</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>20.40187127176439</v>
+        <v>17.87250473118893</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.256035025920486</v>
+        <v>0.426214701272481</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-1.363745661476312</v>
+        <v>0.5231383173583383</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8114</v>
+        <v>8101</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>240.2061951809885</v>
+        <v>212.7461951481096</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>173</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>37.42745349965907</v>
+        <v>35.75252543593254</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.44935833377005</v>
+        <v>30.41452046545894</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.8508673790694599</v>
+        <v>1.132456677495131</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0341218005197903</v>
+        <v>-0.03012462903722957</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8064</v>
+        <v>8104</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>237.4755501936752</v>
+        <v>212.104704525978</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>117.5</v>
+        <v>29.2</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45.09984812889926</v>
+        <v>38.04601633370041</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.00900258175076</v>
+        <v>16.09388016501442</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2915592246543577</v>
+        <v>0.5264338167601188</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-1.54839914585197</v>
+        <v>-0.1253609425796816</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>9955</v>
+        <v>8440</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>234.3424167399418</v>
+        <v>207.525316164572</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>21.1</v>
+        <v>19.6</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>25.15691933963011</v>
+        <v>36.73787233771577</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>21.42057727214098</v>
+        <v>17.54712743694775</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.8342416739941731</v>
+        <v>0.5768580509907351</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1959801439420267</v>
+        <v>-0.04879364825755703</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8476</v>
+        <v>8048</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>232.4530568226226</v>
+        <v>207.3779769478864</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>19.8</v>
+        <v>50.2</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45.18860835656123</v>
+        <v>45.67875926914689</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>19.88633134118078</v>
+        <v>9.38869692756127</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4012830359548555</v>
+        <v>0.4486493118595386</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.1408802886723019</v>
+        <v>-0.0949352988866957</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8481</v>
+        <v>8102</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>232.3953782136098</v>
+        <v>202.245320423372</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>2.391950748436585</v>
+        <v>49.73488266987563</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>21.34742626398174</v>
+        <v>4.805499119181082</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0</v>
+        <v>0.4624722858285174</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-2.605284530010869</v>
+        <v>-0.04014620846847627</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8440</v>
+        <v>9136</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>227.5253161645712</v>
+        <v>201.1123756699125</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>19.6</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>36.73787229018431</v>
+        <v>40.86275320864257</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.54712743133233</v>
+        <v>26.16030380319961</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5768580509907351</v>
+        <v>1.976095081190688</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.04879364822952351</v>
+        <v>-0.05296244423997354</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>volume_break, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8110</v>
+        <v>8097</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>227.2496909983983</v>
+        <v>199.581791964963</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>45.05</v>
+        <v>48.25</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>44.77940580507649</v>
+        <v>43.77704942616348</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.14043450294212</v>
+        <v>12.30468754928894</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.7559299181189851</v>
+        <v>0.3368982156197567</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.4172876003541475</v>
+        <v>0.06356422972157577</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8034</v>
+        <v>8487</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>223.9692841625991</v>
+        <v>193.1934888789404</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>19.65</v>
+        <v>0</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>50.14830657422561</v>
+        <v>2.615589337875448</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14.13722747739685</v>
+        <v>20.53372487614564</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.489392048493493</v>
+        <v>0.0133436018664569</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.05620572448103472</v>
+        <v>-4.455506510800587</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8410</v>
+        <v>8087</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>223.2063249043128</v>
+        <v>190.1468295347593</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>25.95</v>
+        <v>21.6</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>26.92543267605117</v>
+        <v>44.84989919766491</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>44.95799024984046</v>
+        <v>4.638231326701884</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.08195292599467305</v>
+        <v>0.07843536007685754</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.02524819289327063</v>
+        <v>-0.1221550135635383</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8102</v>
+        <v>8411</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>222.245320423372</v>
+        <v>189.9952564605461</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>53</v>
+        <v>11.05</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.73488266475982</v>
+        <v>24.99537747619888</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>4.80549913382193</v>
+        <v>54.13570848070867</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4624722858285174</v>
+        <v>0.1396830556684275</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0401462083563402</v>
+        <v>-0.01012993526380951</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8072</v>
+        <v>8054</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>222.0526648044564</v>
+        <v>188.9403731309597</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>25.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>34.35307075072559</v>
+        <v>41.7835968191705</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>22.51783378150492</v>
+        <v>17.48556336763307</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.074712987338382</v>
+        <v>0.3334492966135028</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1487696335275858</v>
+        <v>-0.3181455300883633</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8097</v>
+        <v>8404</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>219.581791964963</v>
+        <v>186.577243110619</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>48.25</v>
+        <v>13</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>43.7770488640742</v>
+        <v>36.38610924797688</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.30468753128267</v>
+        <v>25.0071801454989</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3368982156197567</v>
+        <v>0.9595825616131861</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.06356422969354414</v>
+        <v>0.04321297238829092</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8499</v>
+        <v>8085</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>219.3321653133017</v>
+        <v>183.2334549607865</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>216</v>
+        <v>14.2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.28510874680374</v>
+        <v>48.07239816187884</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>9.581894092340796</v>
+        <v>18.3350436273894</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5083374663540017</v>
+        <v>0.9977202465283534</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-2.83002951100325</v>
+        <v>-0.07195734742374074</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>9930</v>
+        <v>8114</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>215.0958312161078</v>
+        <v>180.2061951809886</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>58.8</v>
+        <v>173</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>36.97314194727953</v>
+        <v>37.42745320761537</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>24.77513761876725</v>
+        <v>13.44935832706073</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.7417113621673289</v>
+        <v>0.8508673790694599</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0674122889146449</v>
+        <v>0.0341218005197903</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8076</v>
+        <v>8476</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>213.6474473428242</v>
+        <v>172.4530568226226</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>32.19153897023946</v>
+        <v>45.18860843187902</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>41.88493243644027</v>
+        <v>19.88633135205853</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5902964929157671</v>
+        <v>0.4012830359548555</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>1</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.03377475285190584</v>
+        <v>-0.1408802887283729</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8087</v>
+        <v>8481</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>210.1468295347593</v>
+        <v>172.3953782136098</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>44.84989917526288</v>
+        <v>2.391950786901546</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>4.638231294763168</v>
+        <v>21.34742626398174</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.07843536007685754</v>
+        <v>0</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1221550133392637</v>
+        <v>-2.60528452999685</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8067</v>
+        <v>8110</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>195.0069973093181</v>
+        <v>167.2496909983988</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>12.85</v>
+        <v>45.05</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>53.78200837881824</v>
+        <v>44.77940582645369</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.13649663725608</v>
+        <v>16.14043442817854</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.946107028310225</v>
+        <v>0.7559299181189851</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,11 +5923,11 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.3707256805441779</v>
+        <v>-0.4172876001999584</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>185.4585099033234</v>
+        <v>165.4585099033248</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>20.1</v>
@@ -5961,7 +5961,7 @@
         <v>36.22624577946294</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>19.2458511127412</v>
+        <v>19.24585114358833</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.7418923510968206</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.043204341333268</v>
+        <v>-0.04320434129121775</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8940</v>
+        <v>9955</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>172.285770945545</v>
+        <v>164.3424167399417</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>14.65</v>
+        <v>21.1</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>39.56418602749979</v>
+        <v>25.1569191124009</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>12.16817637225105</v>
+        <v>21.42057726522128</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5251502287538152</v>
+        <v>0.8342416739941731</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.03486710739067324</v>
+        <v>-0.1959801438719442</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8482</v>
+        <v>8072</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>171.3961634176659</v>
+        <v>162.0526648044566</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>47.05</v>
+        <v>25.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45.31461390003581</v>
+        <v>34.35307039195756</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>10.46180358531955</v>
+        <v>22.51783378150492</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.28250431016058</v>
+        <v>1.074712987338382</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.2540903874315532</v>
+        <v>-0.148769633331348</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8054</v>
+        <v>8499</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>163.94037313096</v>
+        <v>159.3321653133015</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>216</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>41.78359685160866</v>
+        <v>39.28510870437416</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>17.48556335422377</v>
+        <v>9.581894137565902</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3334492966135028</v>
+        <v>0.5083374663540017</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.3181455305649372</v>
+        <v>-2.83002951002206</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8104</v>
+        <v>8410</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>162.1047045259944</v>
+        <v>133.2063249043128</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>29.2</v>
+        <v>25.95</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>38.04601671072886</v>
+        <v>26.92543260187816</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>16.09388016209975</v>
+        <v>44.9579903022735</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5264338167601188</v>
+        <v>0.08195292599467305</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1253609429020707</v>
+        <v>0.02524819289327063</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8085</v>
+        <v>8076</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>158.2334549607865</v>
+        <v>123.6474473428242</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>14.2</v>
+        <v>20.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>48.07239805236144</v>
+        <v>32.19153897023946</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.33504363664451</v>
+        <v>41.88493240085536</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.9977202465283534</v>
+        <v>0.5902964929157671</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>1</v>
@@ -6241,48 +6241,48 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.07195734735365625</v>
+        <v>-0.03377475285190584</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8222</v>
+        <v>8176</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>141.5936206034293</v>
+        <v>120.1607450088826</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>34.2</v>
+        <v>9.69</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="G110" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>37.66024405161912</v>
+        <v>44.69962840710051</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>8.622028018100426</v>
+        <v>17.49017355986766</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.8849977644733082</v>
+        <v>0.8834480693044595</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.02211894216311994</v>
+        <v>0.005311211726200638</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8105</v>
+        <v>8940</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>133.3335095646957</v>
+        <v>112.285770945545</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>14</v>
+        <v>14.65</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>39.0245018885101</v>
+        <v>39.56418606136646</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.15129898509072</v>
+        <v>12.16817645055302</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.3828948075955512</v>
+        <v>0.5251502287538152</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.05007000361789393</v>
+        <v>-0.03486710739067324</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8488</v>
+        <v>8482</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>133.2231716655587</v>
+        <v>111.3961634176659</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>9.1</v>
+        <v>47.05</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>48.90340405380962</v>
+        <v>45.31461386410489</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.22511791485989</v>
+        <v>10.46180356531092</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.6191285304334693</v>
+        <v>1.28250431016058</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.05817539862287813</v>
+        <v>-0.2540903874315532</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>9110</v>
+        <v>8038</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>122.2989067438914</v>
+        <v>98.46872509533674</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>29.64498058909152</v>
+        <v>42.54181045190148</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>9.843797015528699</v>
+        <v>19.96940144323453</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0</v>
+        <v>0.2933402977278663</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,48 +6453,48 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.3420779706909097</v>
+        <v>-0.3304160508151374</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8176</v>
+        <v>8049</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>120.1607450088829</v>
+        <v>90.27400824512918</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>9.69</v>
+        <v>23.85</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G114" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>44.69962881557695</v>
+        <v>34.12174734504539</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>17.49017349431358</v>
+        <v>19.08118785065288</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.8834480693044595</v>
+        <v>0.7324601502966809</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.005311211695925279</v>
+        <v>-0.03367705651711753</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8038</v>
+        <v>8222</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>118.4687250953379</v>
+        <v>81.5936206034293</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>32.3</v>
+        <v>34.2</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>42.54181026740687</v>
+        <v>37.6602443417593</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>19.96940150090477</v>
+        <v>8.622028058177042</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.2933402977278663</v>
+        <v>0.8849977644733082</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.3304160506749689</v>
+        <v>0.02211894185474572</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8048</v>
+        <v>8105</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>112.3779769478875</v>
+        <v>73.33350956469567</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>50.2</v>
+        <v>14</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>45.67875921022095</v>
+        <v>39.02450187149496</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>9.388696868226052</v>
+        <v>12.15129903562162</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.4486493118595386</v>
+        <v>0.3828948075955512</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.09493529885866459</v>
+        <v>-0.05007000366237957</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>8049</v>
+        <v>8488</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>110.2740082451291</v>
+        <v>73.22317166555862</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>23.85</v>
+        <v>9.1</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>34.12174742863708</v>
+        <v>48.90340408902081</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>19.081187873585</v>
+        <v>18.22511806388843</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.7324601502966809</v>
+        <v>0.6191285304334693</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.03367705654515246</v>
+        <v>0.05817539856680926</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>8472</v>
+        <v>9110</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>103.4149709888362</v>
+        <v>62.29890674389141</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>43.73599821571679</v>
+        <v>29.64498061462774</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>19.27910360687401</v>
+        <v>9.843797005612569</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.8515111024111254</v>
+        <v>0</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,11 +6718,11 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.1181385436235862</v>
+        <v>-0.342077970688106</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>73.49777319818989</v>
+        <v>13.49777319819057</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>37.5</v>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>33.90778236275345</v>
+        <v>33.90778228370259</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>19.15748866951382</v>
+        <v>19.15748869852111</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.5896192788382446</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.009356968283415812</v>
+        <v>-0.009356968269399579</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>8080</v>
+        <v>8472</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>43.3378781593582</v>
+        <v>13.4149709888362</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>28.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>52.14029395597204</v>
+        <v>43.73599827360238</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17.87250470739314</v>
+        <v>19.27910365127281</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.426214701272481</v>
+        <v>0.8515111024111254</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,11 +6824,11 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.5231383175405592</v>
+        <v>0.118138542866673</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
